--- a/exports/trend_1d/IREDA_full_report.xlsx
+++ b/exports/trend_1d/IREDA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>27.63</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H2" t="n">
-        <v>179.6</v>
+        <v>170.65</v>
       </c>
       <c r="I2" t="n">
         <v>173.0726648941761</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K2" t="n">
-        <v>60.36</v>
+        <v>52.37</v>
       </c>
       <c r="L2" t="n">
         <v>14.69</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>19.12</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H3" t="n">
-        <v>149.75</v>
+        <v>157.2</v>
       </c>
       <c r="I3" t="n">
         <v>152.0539827317731</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K3" t="n">
-        <v>12.25</v>
+        <v>7.88</v>
       </c>
       <c r="L3" t="n">
         <v>8.82</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>17.85</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H4" t="n">
-        <v>191.9</v>
+        <v>167.45</v>
       </c>
       <c r="I4" t="n">
         <v>168.1297047263683</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K4" t="n">
-        <v>22.07</v>
+        <v>6.52</v>
       </c>
       <c r="L4" t="n">
         <v>6.42</v>
@@ -669,7 +716,7 @@
         <v>4.13</v>
       </c>
       <c r="N4" t="n">
-        <v>5.14</v>
+        <v>12.74</v>
       </c>
       <c r="O4" t="n">
         <v>4.97</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>24.56</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="H5" t="n">
-        <v>196.11</v>
+        <v>205.35</v>
       </c>
       <c r="I5" t="n">
         <v>201.0778321611089</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>-17.12</v>
+        <v>-22.63</v>
       </c>
       <c r="L5" t="n">
-        <v>22.48</v>
+        <v>24.81</v>
       </c>
       <c r="M5" t="n">
         <v>5.02</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>17</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H6" t="n">
-        <v>254.5</v>
+        <v>238.9</v>
       </c>
       <c r="I6" t="n">
         <v>240.2902705983706</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>23.93</v>
+        <v>16.34</v>
       </c>
       <c r="L6" t="n">
         <v>6.11</v>
       </c>
       <c r="M6" t="n">
-        <v>1.72</v>
+        <v>4.93</v>
       </c>
       <c r="N6" t="n">
-        <v>6.07</v>
+        <v>6.13</v>
       </c>
       <c r="O6" t="n">
         <v>4.71</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>20.32</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="H7" t="n">
-        <v>197.19</v>
+        <v>208.41</v>
       </c>
       <c r="I7" t="n">
         <v>206.5037302334852</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K7" t="n">
-        <v>17.46</v>
+        <v>12.76</v>
       </c>
       <c r="L7" t="n">
         <v>11.26</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.77</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H8" t="n">
-        <v>206.32</v>
+        <v>201.59</v>
       </c>
       <c r="I8" t="n">
         <v>201.7887814358679</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>-1</v>
+        <v>-3.27</v>
       </c>
       <c r="L8" t="n">
         <v>4.04</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>12.95</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="H9" t="n">
-        <v>215.25</v>
+        <v>221.76</v>
       </c>
       <c r="I9" t="n">
         <v>219.1606413765779</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.78</v>
+        <v>-10.01</v>
       </c>
       <c r="L9" t="n">
-        <v>10.37</v>
+        <v>12.93</v>
       </c>
       <c r="M9" t="n">
         <v>0.8100000000000001</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>12.61</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="H10" t="n">
-        <v>200.26</v>
+        <v>196.84</v>
       </c>
       <c r="I10" t="n">
         <v>199.7011569735445</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.699999999999999</v>
+        <v>-11.24</v>
       </c>
       <c r="L10" t="n">
-        <v>11.37</v>
+        <v>12.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="N10" t="n">
         <v>6.91</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>14.98</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H11" t="n">
-        <v>154.82</v>
+        <v>170.04</v>
       </c>
       <c r="I11" t="n">
         <v>160.9174532628331</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K11" t="n">
-        <v>21.35</v>
+        <v>13.62</v>
       </c>
       <c r="L11" t="n">
         <v>6.13</v>
@@ -1068,7 +1199,7 @@
         <v>1.89</v>
       </c>
       <c r="N11" t="n">
-        <v>5.77</v>
+        <v>9.83</v>
       </c>
       <c r="O11" t="n">
         <v>-1.71</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>17.65</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="H12" t="n">
-        <v>175.55</v>
+        <v>167.26</v>
       </c>
       <c r="I12" t="n">
         <v>167.606141478979</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K12" t="n">
-        <v>3.24</v>
+        <v>-1.63</v>
       </c>
       <c r="L12" t="n">
         <v>17.2</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.03</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="H13" t="n">
-        <v>147.35</v>
+        <v>152.37</v>
       </c>
       <c r="I13" t="n">
         <v>151.2726819341311</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K13" t="n">
-        <v>11.9</v>
+        <v>8.9</v>
       </c>
       <c r="L13" t="n">
         <v>4.39</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.27</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H14" t="n">
-        <v>150.27</v>
+        <v>146.28</v>
       </c>
       <c r="I14" t="n">
         <v>149.3300337055321</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.38</v>
+        <v>-4</v>
       </c>
       <c r="L14" t="n">
-        <v>2.94</v>
+        <v>4.18</v>
       </c>
       <c r="M14" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="O14" t="n">
         <v>3.41</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.73</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="H15" t="n">
-        <v>138.1</v>
+        <v>140.99</v>
       </c>
       <c r="I15" t="n">
         <v>140.508630720656</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K15" t="n">
-        <v>5.59</v>
+        <v>3.62</v>
       </c>
       <c r="L15" t="n">
         <v>8.49</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H16" t="n">
-        <v>134.59</v>
+        <v>129.94</v>
       </c>
       <c r="I16" t="n">
         <v>133.6920788585543</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.54</v>
+        <v>-7.84</v>
       </c>
       <c r="L16" t="n">
-        <v>5.11</v>
+        <v>8.18</v>
       </c>
       <c r="M16" t="n">
         <v>0.71</v>
       </c>
       <c r="N16" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
         <v>2.09</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.98</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H17" t="n">
-        <v>123.35</v>
+        <v>126.45</v>
       </c>
       <c r="I17" t="n">
         <v>124.721377296625</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K17" t="n">
-        <v>5.07</v>
+        <v>2.69</v>
       </c>
       <c r="L17" t="n">
         <v>4.77</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>11.25</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="H18" t="n">
-        <v>124.93</v>
+        <v>122.83</v>
       </c>
       <c r="I18" t="n">
         <v>124.557825608515</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2</v>
+        <v>-2.86</v>
       </c>
       <c r="L18" t="n">
-        <v>3.12</v>
+        <v>3.88</v>
       </c>
       <c r="M18" t="n">
         <v>1.18</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.92</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="H19" t="n">
-        <v>127.15</v>
+        <v>130.85</v>
       </c>
       <c r="I19" t="n">
         <v>129.1006209763851</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.52</v>
+        <v>-6.53</v>
       </c>
       <c r="L19" t="n">
-        <v>4.62</v>
+        <v>8.43</v>
       </c>
       <c r="M19" t="n">
         <v>2.35</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="H20" t="n">
-        <v>121.15</v>
+        <v>119.68</v>
       </c>
       <c r="I20" t="n">
         <v>120.5255160280447</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" t="n">
-        <v>-7.41</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>8.44</v>
+        <v>8.75</v>
       </c>
       <c r="M20" t="n">
         <v>1.7</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1641,6 +1892,14 @@
       <c r="Q21" t="n">
         <v>68</v>
       </c>
+      <c r="R21" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2995,7 +3254,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="6">
@@ -3005,7 +3264,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -3015,7 +3274,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
@@ -3025,7 +3284,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3035,7 +3294,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="10">
@@ -3045,7 +3304,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -3085,7 +3344,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.87</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="15">
@@ -3095,7 +3354,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.44</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="16">
@@ -3105,7 +3364,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="17">
@@ -3115,7 +3374,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.36</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="18">
@@ -3125,7 +3384,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="19">
@@ -3135,7 +3394,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.460000000000001</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="20">
@@ -3145,7 +3404,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.42</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="21">
@@ -3155,7 +3414,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.48</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="22">
@@ -3165,7 +3424,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -3185,7 +3444,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="25">
@@ -3205,7 +3464,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.31</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="27">
@@ -3215,7 +3474,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.93</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="28">
